--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c6fb59ddac9459a3/Desktop/excel776/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7416387-5979-450E-903C-54583C26F1E5}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22072AA5-D29F-42A2-AD45-AA722825B115}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>medium</t>
+  </si>
+  <si>
+    <t>high</t>
   </si>
 </sst>
 </file>
@@ -887,7 +890,7 @@
   <dimension ref="A1:N401"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
     <col min="2" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
@@ -1183,157 +1186,310 @@
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B10" s="14">
+        <v>400</v>
+      </c>
+      <c r="C10" s="14">
+        <v>20</v>
+      </c>
+      <c r="D10" s="14">
+        <v>190</v>
+      </c>
+      <c r="E10" s="14">
+        <v>110</v>
+      </c>
+      <c r="F10" s="14">
+        <v>250</v>
+      </c>
+      <c r="G10" s="14">
+        <v>5</v>
+      </c>
+      <c r="H10" s="14">
+        <v>20</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>10</v>
+      </c>
+      <c r="D11" s="14">
+        <v>200</v>
+      </c>
+      <c r="E11" s="14">
+        <v>100</v>
+      </c>
+      <c r="F11" s="14">
+        <v>400</v>
+      </c>
+      <c r="G11" s="14">
+        <v>8</v>
+      </c>
+      <c r="H11" s="14">
+        <v>30</v>
+      </c>
+      <c r="I11" s="15">
+        <v>1240</v>
+      </c>
+      <c r="J11" s="15">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N11" s="17"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B12" s="14">
+        <v>360</v>
+      </c>
+      <c r="C12" s="14">
+        <v>20</v>
+      </c>
+      <c r="D12" s="14">
+        <v>100</v>
+      </c>
+      <c r="E12" s="14">
+        <v>50</v>
+      </c>
+      <c r="F12" s="14">
+        <v>250</v>
+      </c>
+      <c r="G12" s="14">
+        <v>5</v>
+      </c>
+      <c r="H12" s="14">
+        <v>35</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>815</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+        <v>625</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="17"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B13" s="14">
+        <v>360</v>
+      </c>
+      <c r="C13" s="14">
+        <v>20</v>
+      </c>
+      <c r="D13" s="14">
+        <v>160</v>
+      </c>
+      <c r="E13" s="14">
+        <v>110</v>
+      </c>
+      <c r="F13" s="14">
+        <v>200</v>
+      </c>
+      <c r="G13" s="14">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14">
+        <v>30</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+        <v>560</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B14" s="14">
+        <v>360</v>
+      </c>
+      <c r="C14" s="14">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14">
+        <v>150</v>
+      </c>
+      <c r="E14" s="14">
+        <v>100</v>
+      </c>
+      <c r="F14" s="14">
+        <v>150</v>
+      </c>
+      <c r="G14" s="14">
+        <v>3</v>
+      </c>
+      <c r="H14" s="14">
+        <v>40</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N14" s="17"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>300</v>
+      </c>
+      <c r="E15" s="14">
+        <v>180</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" s="14">
+        <v>50</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+        <v>470</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N15" s="17"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>300</v>
+      </c>
+      <c r="E16" s="14">
+        <v>200</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="14">
+        <v>40</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+        <v>460</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
